--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1339 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +923,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1092,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1133,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2856,1121 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62773D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -884,12 +884,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3597,7 +3597,7 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3974,6 +3974,232 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq40，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1219,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1474,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1624,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1696,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1735,7 +1759,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1807,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1918,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2218,12 +2242,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq41推进至seq49，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2251,18 +2275,30 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>08:21</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2362,7 +2398,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2509,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2620,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2731,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2842,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2953,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,7 +3064,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3139,7 +3175,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3286,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3361,7 +3397,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3472,7 +3508,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3583,7 +3619,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3694,7 +3730,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3805,7 +3841,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3920,7 +3956,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4031,7 +4067,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4146,7 +4182,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4200,6 +4236,684 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1687,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1764,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1798,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1831,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1855,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1909,12 +1925,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq49推进至seq58，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1942,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1950,10 +1966,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2020,32 +2048,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2053,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2077,33 +2109,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2167,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2164,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2188,33 +2228,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2291,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq41推进至seq49，推进8站，达到≥2站确认条件</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq41推进至seq52，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2275,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,32 +2409,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2398,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2422,33 +2470,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2548,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2620,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2659,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2698,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2731,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2755,33 +2811,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2881,7 +2941,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2920,32 +2980,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2953,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2977,33 +3041,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3031,32 +3099,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3064,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3088,17 +3160,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3108,13 +3180,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3286,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3397,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3436,7 +3512,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3508,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3619,7 +3695,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3730,7 +3806,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3841,7 +3917,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3895,7 +3971,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3956,7 +4032,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4067,7 +4143,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4182,7 +4258,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4293,7 +4369,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4404,7 +4480,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4458,7 +4534,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4595,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4573,7 +4649,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4710,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4688,7 +4764,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4825,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4860,7 +4936,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4904,11 +4980,1149 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr"/>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,18 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2147,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2266,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2672,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2990,24 +2998,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3017,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3066,12 +3074,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3109,24 +3117,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3175,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3218,32 +3226,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3251,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3275,17 +3287,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3295,13 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3329,32 +3345,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3362,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3386,17 +3406,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3406,13 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3440,32 +3464,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3473,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3497,17 +3525,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3517,13 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3662,32 +3694,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3695,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3719,33 +3755,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3773,32 +3813,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3806,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3830,33 +3874,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3884,32 +3932,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3917,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3941,17 +3993,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3961,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3999,32 +4051,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4032,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4056,17 +4112,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4076,13 +4132,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4110,32 +4170,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4143,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4167,37 +4231,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4225,32 +4289,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4258,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4282,33 +4350,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4336,12 +4408,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq52，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4369,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4377,10 +4449,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr"/>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4480,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4534,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4649,7 +4737,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4764,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4864,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4936,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4990,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5105,7 +5193,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5220,7 +5308,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5369,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5335,7 +5423,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5484,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5507,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5561,7 +5649,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5710,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5676,7 +5764,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5825,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5848,7 +5936,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5959,7 +6047,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6008,12 +6096,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>168.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6021,22 +6109,22 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6069,12 +6157,12 @@
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6088,41 +6176,731 @@
       <c r="T49" s="2" t="inlineStr"/>
       <c r="U49" s="2" t="inlineStr">
         <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
           <t>11:20</t>
         </is>
       </c>
-      <c r="V49" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W49" s="2" t="inlineStr">
+      <c r="W50" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X49" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z49" s="2" t="inlineStr">
+      <c r="Z50" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr"/>
-      <c r="AC49" s="2" t="inlineStr">
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
         </is>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,13 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2032,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2137,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2378,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2393,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,13 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2727,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2738,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2968,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3079,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3555,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3674,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3904,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4261,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4380,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4421,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq52，推进23站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4441,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4515,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4535,32 +4543,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4568,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4592,17 +4604,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4612,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4737,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4837,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4852,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4880,32 +4892,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4913,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,17 +4953,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4957,13 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4991,32 +5011,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5024,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5048,17 +5072,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5068,17 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5106,32 +5130,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5139,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5163,17 +5191,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5183,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5221,32 +5249,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5254,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5278,17 +5310,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5298,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5336,32 +5368,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5369,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5393,37 +5429,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5451,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5484,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5508,17 +5548,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5528,13 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5649,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5764,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5864,7 +5908,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5875,7 +5919,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5986,7 +6030,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6091,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6101,7 +6145,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6216,7 +6260,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6321,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6331,7 +6375,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6446,7 +6490,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6561,7 +6605,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6676,7 +6720,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6781,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6791,7 +6835,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6896,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6896,13 +6940,691 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr"/>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>—/28</t>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,14 +823,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,13 +2732,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2851,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,13 +2966,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,17 +3786,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3858,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,14 +4024,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -4031,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4864,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5578,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5606,32 +5614,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5639,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5663,17 +5675,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5683,17 +5695,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5754,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,17 +5794,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5798,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5836,32 +5852,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5869,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,17 +5913,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5913,13 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5980,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6004,17 +6032,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6024,13 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6058,32 +6090,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6091,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6115,37 +6151,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6173,32 +6209,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6206,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6230,37 +6270,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6288,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6321,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6345,17 +6389,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6365,17 +6409,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6436,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6460,32 +6508,32 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6518,32 +6566,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6551,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6575,17 +6627,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6595,17 +6647,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6666,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6720,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6835,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6950,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7065,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7348,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7402,7 +7454,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7574,7 +7626,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7618,13 +7670,592 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,17 +4976,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,14 +5214,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6457,24 +6457,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6576,24 +6576,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6685,32 +6685,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,37 +6746,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6915,32 +6919,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6948,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,32 +6980,32 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7030,32 +7038,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7063,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7087,17 +7099,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7107,17 +7119,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7157,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7178,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7186,10 +7198,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -7289,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7515,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7626,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7971,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8025,7 +8053,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8135,12 +8163,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8229,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8259,6 +8287,466 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2026,13 +2026,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2140,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -2151,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2861,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4642,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4867,7 +4871,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,7 +4990,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5110,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5229,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,14 +5337,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -5348,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5467,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5705,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5824,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6127,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6181,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6300,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6776,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6929,24 +6933,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6956,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7005,7 +7009,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7048,24 +7052,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7075,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7124,7 +7128,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7162,7 +7166,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7190,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7284,32 +7288,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7317,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7349,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7361,13 +7369,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7482,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7654,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7769,7 +7781,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7884,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7938,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8065,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8168,7 +8180,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8283,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8398,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8513,7 +8525,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8623,7 +8635,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8689,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8743,7 +8755,122 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC71"/>
+  <dimension ref="A1:AC76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,13 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2740,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,14 +2854,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -2865,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3099,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3208,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3686,7 +3690,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4404,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4520,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4527,7 +4531,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,12 +4875,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5237,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5352,7 +5356,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,17 +5465,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,14 +5817,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -5828,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7052,19 +7056,19 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -7079,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7128,12 +7132,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7170,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7194,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7260,7 +7264,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7298,24 +7302,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7325,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7374,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7407,32 +7411,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7440,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7472,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7484,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7522,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7555,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7591,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7599,13 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -7633,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7666,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7690,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7710,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7748,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7781,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7805,17 +7829,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7825,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7863,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7896,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7920,17 +7948,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7940,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8065,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8180,7 +8208,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8295,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8410,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8525,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8640,7 +8668,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8755,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8763,22 +8791,22 @@
       <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8811,12 +8839,12 @@
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8830,47 +8858,610 @@
       <c r="T71" s="2" t="inlineStr"/>
       <c r="U71" s="2" t="inlineStr">
         <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>15:35</t>
         </is>
       </c>
-      <c r="V71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W71" s="2" t="inlineStr">
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X71" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y71" s="2" t="inlineStr">
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z72" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
         </is>
       </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>23/29</t>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC76"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,14 +1775,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,14 +3564,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,14 +5103,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>145.0</t>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,17 +6179,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,14 +6412,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>136.0</t>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6774,17 +6774,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7897,12 +7897,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8006,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8039,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8067,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8121,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8154,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8186,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8198,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8244,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8269,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,17 +8305,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8313,17 +8325,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>138.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8384,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8408,17 +8424,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8428,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8553,7 +8569,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8844,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8959,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9074,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9185,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9243,7 +9259,7 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -9296,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9340,13 +9356,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>169.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9354,22 +9374,22 @@
       <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9402,12 +9422,12 @@
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9421,47 +9441,1078 @@
       <c r="T76" s="2" t="inlineStr"/>
       <c r="U76" s="2" t="inlineStr">
         <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
           <t>16:01</t>
         </is>
       </c>
-      <c r="V76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W76" s="2" t="inlineStr">
+      <c r="W77" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y76" s="2" t="inlineStr">
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z76" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
         </is>
       </c>
-      <c r="AC76" s="2" t="inlineStr">
-        <is>
-          <t>19/30</t>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>20/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>133.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>9/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,22 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>155.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,13 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,17 +4036,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4350,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4399,7 +4403,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4639,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4869,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,12 +4993,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5183,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5302,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,17 +5350,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>155.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,7 +5940,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5951,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6611,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,7 +6783,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6845,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6964,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,12 +7012,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7126,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7329,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,22 +7372,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7686,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7729,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7740,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -8254,12 +8258,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
@@ -8281,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8320,17 +8324,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>138.3</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8373,19 +8377,19 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -8400,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8449,7 +8453,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8482,32 +8486,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8515,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,37 +8547,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8597,32 +8605,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8630,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,17 +8666,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8674,12 +8686,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8745,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8827,32 +8839,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8860,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,37 +8900,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -8942,32 +8958,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8975,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8999,17 +9019,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9019,17 +9039,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>155.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -9057,12 +9077,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9090,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9098,10 +9118,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
-      <c r="R73" s="2" t="inlineStr"/>
-      <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -9366,7 +9402,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -9394,32 +9430,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9427,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,17 +9491,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9471,13 +9511,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9653,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9768,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9883,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9998,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10113,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10167,7 +10211,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10228,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10343,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10405,7 +10449,7 @@
       <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -10415,7 +10459,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -10453,12 +10497,12 @@
       <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10472,47 +10516,737 @@
       <c r="T85" s="2" t="inlineStr"/>
       <c r="U85" s="2" t="inlineStr">
         <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
           <t>17:40</t>
         </is>
       </c>
-      <c r="V85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W85" s="2" t="inlineStr">
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X85" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y85" s="2" t="inlineStr">
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z85" s="2" t="inlineStr">
+      <c r="Z87" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
+      <c r="AB87" s="2" t="inlineStr">
         <is>
           <t>133.7</t>
         </is>
       </c>
-      <c r="AC85" s="2" t="inlineStr">
+      <c r="AC87" s="2" t="inlineStr">
         <is>
           <t>9/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>155.3</t>
+          <t>153.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2391,17 +2391,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,17 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4535,7 +4535,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>155.3</t>
+          <t>153.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,14 +6297,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7615,17 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,14 +7967,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>131.0</t>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8968,24 +8968,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>163分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9044,12 +9044,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>155.3</t>
+          <t>153.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq45，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       <c r="AB74" s="2" t="inlineStr"/>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -9440,24 +9440,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9549,32 +9549,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9582,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,17 +9610,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9626,17 +9630,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9664,32 +9668,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9697,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,17 +9729,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9741,17 +9749,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9851,7 +9859,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9866,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9966,7 +9974,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9981,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10096,7 +10104,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10211,7 +10219,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10326,7 +10334,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10441,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10556,7 +10564,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10671,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10786,7 +10794,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10901,7 +10909,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11016,7 +11024,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11131,7 +11139,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11246,7 +11254,808 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>4/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>17:51</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>—/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>12/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>17/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,17 +4754,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9787,32 +9787,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9820,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9844,17 +9848,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9864,17 +9868,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9902,32 +9906,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9935,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,17 +9967,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9979,17 +9987,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -10017,32 +10025,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10050,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,32 +10086,32 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10132,32 +10144,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10165,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,37 +10205,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10247,32 +10263,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10280,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10304,37 +10324,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10510,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10564,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10740,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10855,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10909,7 +10929,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11024,7 +11044,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11200,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11254,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11315,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11369,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11484,7 +11504,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11656,7 +11676,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11771,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11825,7 +11845,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11930,17 +11950,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>145.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12045,17 +12065,707 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>20/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>153.3</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>25/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>8/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
           <t>145.0</t>
         </is>
       </c>
-      <c r="AC98" s="2" t="inlineStr">
-        <is>
-          <t>17/31</t>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>16/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>155.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>26/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>23/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>18/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC104"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2264,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,22 +2505,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,17 +4874,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,14 +6178,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8086,14 +8086,14 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>140.0</t>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -10497,32 +10497,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10530,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10554,17 +10558,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10574,17 +10578,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10612,32 +10616,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10645,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10669,37 +10677,37 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>151.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10727,32 +10735,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10760,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,17 +10796,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10804,17 +10816,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10842,32 +10854,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10875,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10899,17 +10915,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10919,17 +10935,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -10990,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11044,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11335,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11450,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11565,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11676,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11730,7 +11746,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11906,7 +11922,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12021,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12136,7 +12152,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12251,7 +12267,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12366,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12481,7 +12497,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12596,7 +12612,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12650,7 +12666,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12658,22 +12674,22 @@
       <c r="A104" s="2" t="inlineStr"/>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -12706,12 +12722,12 @@
       <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12725,47 +12741,277 @@
       <c r="T104" s="2" t="inlineStr"/>
       <c r="U104" s="2" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>12/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W104" s="2" t="inlineStr">
+      <c r="W105" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X104" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y104" s="2" t="inlineStr">
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z104" s="2" t="inlineStr">
+      <c r="Z105" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA104" s="2" t="inlineStr">
+      <c r="AA105" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB104" s="2" t="inlineStr">
+      <c r="AB105" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
         </is>
       </c>
-      <c r="AC104" s="2" t="inlineStr">
+      <c r="AC105" s="2" t="inlineStr">
         <is>
           <t>18/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>151.3</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>24/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8567,17 +8567,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -10626,24 +10626,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10702,12 +10702,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -10745,24 +10745,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>136.8</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10864,24 +10864,24 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>143.2</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10973,32 +10973,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11006,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11030,17 +11034,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11050,17 +11054,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -11088,32 +11092,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11121,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11145,17 +11153,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11165,17 +11173,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -11290,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11351,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11390,7 +11398,7 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11405,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11520,7 +11528,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11692,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11807,7 +11815,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11889,12 +11897,12 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -11922,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11930,10 +11938,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q97" s="2" t="inlineStr"/>
-      <c r="R97" s="2" t="inlineStr"/>
-      <c r="S97" s="2" t="inlineStr"/>
-      <c r="T97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12037,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12152,7 +12176,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12267,7 +12291,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12321,7 +12345,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12406,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12497,7 +12521,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12612,7 +12636,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12727,7 +12751,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12842,7 +12866,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12957,7 +12981,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13006,12 +13030,127 @@
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>151.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>22/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>2/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-22-浦东35路.xlsx
+++ b/data/export/2026-10-22-浦东35路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,12 +6064,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -9467,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9511,17 +9511,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9987,17 +9987,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10945,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -10995,12 +10995,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -11102,24 +11102,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11326,32 +11326,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11359,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11383,17 +11387,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11403,12 +11407,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11441,32 +11445,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11474,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11498,17 +11506,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11518,17 +11526,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11556,32 +11564,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -11589,7 +11601,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11613,17 +11625,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11633,13 +11645,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB94" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -11667,32 +11683,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11700,7 +11720,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11724,17 +11744,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11744,17 +11764,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11802,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11815,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11839,17 +11863,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11859,17 +11883,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11926,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -11930,7 +11954,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12000,7 +12024,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12028,32 +12052,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12061,7 +12089,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12085,17 +12113,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12105,17 +12133,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12176,7 +12204,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12230,7 +12258,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -12258,12 +12286,12 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12291,7 +12319,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12299,10 +12327,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr"/>
-      <c r="R100" s="2" t="inlineStr"/>
-      <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12406,7 +12450,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12460,7 +12504,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>16/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12565,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12575,7 +12619,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12680,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12690,7 +12734,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12795,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12805,7 +12849,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12910,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12920,7 +12964,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12981,7 +13025,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13035,7 +13079,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13140,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13140,12 +13184,12 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
